--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2">
         <v>20</v>
@@ -1125,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>30</v>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris WebOffice" lastEdited="6" lowestEdited="6" rupBuild=""/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ENEMY" sheetId="2" r:id="rId1"/>
+    <sheet name="EnemyData" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>key</t>
   </si>
@@ -61,75 +57,358 @@
   </si>
   <si>
     <t>Boss_zombie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Zombie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="21">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -144,47 +423,327 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -474,24 +1033,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.59765625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="1" max="1" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="2" width="12.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="2" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="2" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="2" width="19.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="2" width="16.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="2" width="14.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="2" width="15.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="16384" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +1076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>2001</v>
       </c>
@@ -543,7 +1102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>2002</v>
       </c>
@@ -569,7 +1128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>2003</v>
       </c>
@@ -595,7 +1154,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>2004</v>
       </c>
@@ -623,7 +1182,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris WebOffice" lastEdited="6" lowestEdited="6" rupBuild=""/>
+  <fileVersion appName="Polaris WebOffice" lastEdited="4" lowestEdited="4" rupBuild=""/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyData" sheetId="2" r:id="rId1"/>
+    <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="152511"/>
@@ -15,51 +15,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>UnitName</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>EnemyID</t>
+  </si>
+  <si>
+    <t>EnemyName</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>AttackPower</t>
   </si>
   <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
-    <t>MovementSpeed</t>
+    <t>SpawnCount</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Zombie1</t>
+  </si>
+  <si>
+    <t>Zombie2</t>
+  </si>
+  <si>
+    <t>Zombie3</t>
+  </si>
+  <si>
+    <t>Boss_Zombie</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>RewardMoney</t>
-  </si>
-  <si>
-    <t>EnemyType</t>
-  </si>
-  <si>
-    <t>1_zombie</t>
-  </si>
-  <si>
-    <t>2_zombie</t>
-  </si>
-  <si>
-    <t>3_zombie</t>
-  </si>
-  <si>
-    <t>boss_zombie</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Boss_zombie</t>
-  </si>
-  <si>
-    <t>Zombie</t>
   </si>
 </sst>
 </file>
@@ -99,12 +96,6 @@
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
       <color rgb="FFFF0000"/>
     </font>
     <font>
@@ -197,6 +188,12 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -536,161 +533,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -712,6 +703,7 @@
     <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
     <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
     <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="강조색1" xfId="24" builtinId="29"/>
     <cellStyle name="강조색2" xfId="28" builtinId="33"/>
     <cellStyle name="강조색3" xfId="32" builtinId="37"/>
@@ -722,14 +714,14 @@
     <cellStyle name="계산" xfId="17" builtinId="22"/>
     <cellStyle name="나쁨" xfId="22" builtinId="27"/>
     <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
     <cellStyle name="보통" xfId="23" builtinId="28"/>
     <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
     <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
     <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
     <cellStyle name="요약" xfId="20" builtinId="25"/>
     <cellStyle name="입력" xfId="15" builtinId="20"/>
     <cellStyle name="제목" xfId="10" builtinId="15"/>
@@ -739,18 +731,17 @@
     <cellStyle name="제목4" xfId="14" builtinId="19"/>
     <cellStyle name="좋음" xfId="21" builtinId="26"/>
     <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -788,7 +779,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -822,7 +813,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -857,10 +847,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1034,23 +1023,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
-  <cols>
-    <col min="1" max="1" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="2" width="12.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="2" width="13.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="2" width="13.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="2" width="19.62999916" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="7" style="2" width="16.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="2" width="14.88000011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="9" style="2" width="15.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="10" max="10" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="11" max="16384" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
-  </cols>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1069,115 +1045,123 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="C2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2">
-        <v>2001</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" s="2">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="C3" s="0">
+        <v>50</v>
+      </c>
+      <c r="D3" s="0">
         <v>1</v>
       </c>
-      <c r="F2" s="2">
+      <c r="E3" s="0">
+        <v>10</v>
+      </c>
+      <c r="F3" s="0">
+        <v>5</v>
+      </c>
+      <c r="G3" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="0">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0">
+        <v>75</v>
+      </c>
+      <c r="D4" s="0">
+        <v>0.8</v>
+      </c>
+      <c r="E4" s="0">
+        <v>20</v>
+      </c>
+      <c r="F4" s="0">
         <v>3</v>
       </c>
-      <c r="G2" s="2">
-        <v>5</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
+      <c r="G4" s="0">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="5" spans="1:7">
+      <c r="A5" s="0">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="0">
+        <v>100</v>
+      </c>
+      <c r="D5" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="0">
+        <v>15</v>
+      </c>
+      <c r="F5" s="0">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="0">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="0">
+        <v>500</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="E6" s="0">
         <v>50</v>
       </c>
-      <c r="D3" s="2">
-        <v>25</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-      <c r="D4" s="2">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D5" s="2">
-        <v>300</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>300</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
+      <c r="F6" s="0">
+        <v>4</v>
+      </c>
+      <c r="G6" s="0">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris WebOffice" lastEdited="4" lowestEdited="4" rupBuild=""/>
+  <fileVersion appName="Polaris WebOffice" lastEdited="6" lowestEdited="6" rupBuild=""/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
+    <sheet name="EnemyData" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="152511"/>
@@ -15,48 +15,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>EnemyID</t>
-  </si>
-  <si>
-    <t>EnemyName</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>UnitName</t>
   </si>
   <si>
     <t>Health</t>
   </si>
   <si>
-    <t>Speed</t>
-  </si>
-  <si>
     <t>AttackPower</t>
   </si>
   <si>
-    <t>SpawnCount</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Zombie1</t>
-  </si>
-  <si>
-    <t>Zombie2</t>
-  </si>
-  <si>
-    <t>Zombie3</t>
-  </si>
-  <si>
-    <t>Boss_Zombie</t>
-  </si>
-  <si>
-    <t>float</t>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>MovementSpeed</t>
   </si>
   <si>
     <t>RewardMoney</t>
+  </si>
+  <si>
+    <t>EnemyType</t>
+  </si>
+  <si>
+    <t>1_zombie</t>
+  </si>
+  <si>
+    <t>2_zombie</t>
+  </si>
+  <si>
+    <t>3_zombie</t>
+  </si>
+  <si>
+    <t>boss_zombie</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Boss_zombie</t>
+  </si>
+  <si>
+    <t>Zombie</t>
   </si>
 </sst>
 </file>
@@ -96,6 +99,12 @@
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FFFF0000"/>
     </font>
     <font>
@@ -188,12 +197,6 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -533,6 +536,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -548,140 +557,140 @@
     <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -703,7 +712,6 @@
     <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
     <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
     <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="강조색1" xfId="24" builtinId="29"/>
     <cellStyle name="강조색2" xfId="28" builtinId="33"/>
     <cellStyle name="강조색3" xfId="32" builtinId="37"/>
@@ -714,14 +722,14 @@
     <cellStyle name="계산" xfId="17" builtinId="22"/>
     <cellStyle name="나쁨" xfId="22" builtinId="27"/>
     <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
     <cellStyle name="보통" xfId="23" builtinId="28"/>
     <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
     <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
     <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
-    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="요약" xfId="20" builtinId="25"/>
     <cellStyle name="입력" xfId="15" builtinId="20"/>
     <cellStyle name="제목" xfId="10" builtinId="15"/>
@@ -731,17 +739,18 @@
     <cellStyle name="제목4" xfId="14" builtinId="19"/>
     <cellStyle name="좋음" xfId="21" builtinId="26"/>
     <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="2" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -779,7 +788,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -813,6 +822,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -847,9 +857,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1023,10 +1034,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
+  <cols>
+    <col min="1" max="1" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="2" width="12.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="2" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="2" width="13.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="2" width="19.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="2" width="16.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="2" width="14.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="2" width="15.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="16384" style="2" width="9.00500011" customWidth="1" outlineLevel="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,123 +1069,115 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>300</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>300</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="0">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="0">
-        <v>50</v>
-      </c>
-      <c r="D3" s="0">
-        <v>1</v>
-      </c>
-      <c r="E3" s="0">
-        <v>10</v>
-      </c>
-      <c r="F3" s="0">
-        <v>5</v>
-      </c>
-      <c r="G3" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="0">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="0">
-        <v>75</v>
-      </c>
-      <c r="D4" s="0">
-        <v>0.8</v>
-      </c>
-      <c r="E4" s="0">
-        <v>20</v>
-      </c>
-      <c r="F4" s="0">
-        <v>3</v>
-      </c>
-      <c r="G4" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="0">
-        <v>3</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="0">
-        <v>100</v>
-      </c>
-      <c r="D5" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="0">
-        <v>15</v>
-      </c>
-      <c r="F5" s="0">
-        <v>1</v>
-      </c>
-      <c r="G5" s="0">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="0">
-        <v>4</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="0">
-        <v>500</v>
-      </c>
-      <c r="D6" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="E6" s="0">
-        <v>50</v>
-      </c>
-      <c r="F6" s="0">
-        <v>4</v>
-      </c>
-      <c r="G6" s="0">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -63,8 +63,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+  <numFmts count="2">
+    <numFmt numFmtId="64" formatCode="0.00_ "/>
+    <numFmt numFmtId="65" formatCode="0.000_ "/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -159,13 +162,6 @@
       <color rgb="FFFA7D00"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
@@ -188,12 +184,6 @@
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
       <color theme="0"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <i/>
@@ -434,7 +424,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -443,7 +432,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -452,7 +440,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -461,7 +448,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -476,7 +462,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -491,7 +476,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -506,7 +490,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -515,7 +498,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -526,7 +508,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -590,99 +571,101 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="65" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
@@ -1057,13 +1040,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>6</v>
@@ -1079,13 +1062,13 @@
       <c r="B3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3" s="3">
         <v>50</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="3">
         <v>10</v>
       </c>
       <c r="F3" s="0">
@@ -1102,13 +1085,13 @@
       <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4" s="3">
         <v>75</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4" s="3">
         <v>0.8</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="3">
         <v>20</v>
       </c>
       <c r="F4" s="0">
@@ -1125,13 +1108,13 @@
       <c r="B5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5" s="3">
         <v>100</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5" s="3">
         <v>0.5</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="3">
         <v>15</v>
       </c>
       <c r="F5" s="0">
@@ -1148,13 +1131,13 @@
       <c r="B6" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6" s="3">
         <v>500</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6" s="3">
         <v>1.2</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="3">
         <v>50</v>
       </c>
       <c r="F6" s="0">

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8279BE-A3A2-46C7-9619-7083C80FD927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49E28A-81F5-4479-BE32-7EE78D8160FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -162,7 +162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -474,8 +474,8 @@
   <cols>
     <col min="1" max="1" width="9.625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.25" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="3" bestFit="1" customWidth="1"/>
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -548,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -559,7 +559,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="4">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4">
         <v>0.8</v>
@@ -571,7 +571,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -582,7 +582,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D5" s="4">
         <v>0.5</v>
@@ -594,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -605,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="4">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="D6" s="4">
         <v>1.2</v>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49E28A-81F5-4479-BE32-7EE78D8160FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Health</t>
   </si>
@@ -59,70 +54,350 @@
   </si>
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="64" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+  <fonts count="19">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -137,50 +412,321 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -468,21 +1014,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="1" style="3" width="9.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="3" width="15.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="3" width="14.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="16383" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16384" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -505,7 +1052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -528,9 +1075,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
-        <v>2001</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
@@ -551,9 +1098,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="3">
-        <v>2002</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -574,9 +1121,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="3">
-        <v>2003</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>8</v>
@@ -597,9 +1144,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="3">
-        <v>2004</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
@@ -622,7 +1169,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C14F5A4-1B57-4A28-9828-1822C830BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -73,7 +72,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
@@ -486,22 +485,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="9.59765625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.09765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.19921875" style="3" customWidth="1"/>
     <col min="7" max="7" width="14" style="3" customWidth="1"/>
     <col min="8" max="16383" width="9" style="3" customWidth="1"/>
     <col min="16384" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -524,7 +523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -547,7 +546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -558,7 +557,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="6">
         <v>1</v>
@@ -570,7 +569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -578,22 +577,22 @@
         <v>5</v>
       </c>
       <c r="C4" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="6">
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -601,22 +600,22 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="6">
         <v>1</v>
       </c>
       <c r="F5" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -624,10 +623,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -636,12 +635,12 @@
         <v>50</v>
       </c>
       <c r="G6" s="3">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Health</t>
   </si>
@@ -58,82 +54,369 @@
   </si>
   <si>
     <t>MovementSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AttackSpeed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyType</t>
+  </si>
+  <si>
+    <t>Melee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+  <fonts count="21">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -148,26 +431,270 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -176,28 +703,64 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -485,22 +1048,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.09765625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.09765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.09765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.19921875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14" style="3" customWidth="1"/>
-    <col min="8" max="16383" width="9" style="3" customWidth="1"/>
-    <col min="16384" max="16384" width="9" style="3"/>
+    <col min="1" max="1" style="3" width="9.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="3" width="15.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="3" width="17.12999916" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="16383" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16384" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -522,8 +1085,11 @@
       <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -545,8 +1111,11 @@
       <c r="G2" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -568,8 +1137,11 @@
       <c r="G3" s="3">
         <v>20</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -591,8 +1163,11 @@
       <c r="G4" s="3">
         <v>25</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -614,8 +1189,11 @@
       <c r="G5" s="3">
         <v>30</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -636,11 +1214,14 @@
       </c>
       <c r="G6" s="3">
         <v>300</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Health</t>
   </si>
@@ -80,13 +76,9 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>rc1</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -97,22 +89,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>rc2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
     </r>
   </si>
   <si>
@@ -124,31 +102,15 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>rc3</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
   </si>
   <si>
     <t>Boss_Orc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Skeleton1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Skeleton2</t>
@@ -165,17 +127,12 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>oss_Skeleton</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Reaper1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Reaper2</t>
@@ -192,17 +149,12 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>oss_Reaper</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Minotaur1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Minotaur2</t>
@@ -219,13 +171,9 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>oss_Minotaur</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>FallenAngel2</t>
@@ -235,7 +183,6 @@
   </si>
   <si>
     <t>FallenAngel1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -246,9 +193,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>oss_</t>
     </r>
@@ -257,86 +201,363 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <scheme val="minor"/>
       </rPr>
       <t>FallenAngel</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+  <fonts count="21">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -351,26 +572,270 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -379,28 +844,64 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -688,22 +1189,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.09765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.09765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.59765625" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" style="3" width="9.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="3" width="15.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="3" width="15.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="3" width="17.12999916" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -729,7 +1230,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -755,7 +1256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -781,7 +1282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -807,7 +1308,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -833,7 +1334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -859,7 +1360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -885,7 +1386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -911,7 +1412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -937,7 +1438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -963,7 +1464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -986,10 +1487,10 @@
         <v>20</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1015,7 +1516,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1041,7 +1542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1067,7 +1568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1093,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1119,7 +1620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1145,7 +1646,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1171,7 +1672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1197,7 +1698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1223,7 +1724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1249,7 +1750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1275,7 +1776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1301,7 +1802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1327,7 +1828,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1353,7 +1854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1380,8 +1881,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>Health</t>
   </si>
@@ -76,6 +80,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>rc1</t>
     </r>
@@ -89,6 +95,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>rc2</t>
     </r>
@@ -102,6 +110,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>rc3</t>
     </r>
@@ -127,6 +137,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>oss_Skeleton</t>
     </r>
@@ -149,6 +161,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>oss_Reaper</t>
     </r>
@@ -171,6 +185,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>oss_Minotaur</t>
     </r>
@@ -193,6 +209,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>oss_</t>
     </r>
@@ -201,363 +219,102 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>FallenAngel</t>
     </r>
   </si>
   <si>
-    <t>Ranged</t>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>elee</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="1"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="10"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
-      <color theme="11"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFF0000"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="3"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F76"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF3F3F3F"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FFFA7D00"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF006100"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C0006"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF9C6500"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color theme="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11.0"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-      <color rgb="FF7F7F7F"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599990"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399980"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -572,270 +329,26 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399980"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -844,64 +357,31 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
-    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
-    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
-    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
-    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
-    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
-    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
-    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
-    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
-    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
-    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
-    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
-    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
-    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
-    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
-    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
-    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
-    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
-    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
-    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
-    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
-    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
-    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
-    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
-    <cellStyle name="경고문" xfId="9" builtinId="11"/>
-    <cellStyle name="계산" xfId="17" builtinId="22"/>
-    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
-    <cellStyle name="메모" xfId="8" builtinId="10"/>
-    <cellStyle name="백분율" xfId="5" builtinId="5"/>
-    <cellStyle name="보통" xfId="23" builtinId="28"/>
-    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
-    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
-    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+  <cellStyles count="3">
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="요약" xfId="20" builtinId="25"/>
-    <cellStyle name="입력" xfId="15" builtinId="20"/>
-    <cellStyle name="제목" xfId="10" builtinId="15"/>
-    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
-    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
-    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
-    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
-    <cellStyle name="좋음" xfId="21" builtinId="26"/>
-    <cellStyle name="출력" xfId="16" builtinId="21"/>
-    <cellStyle name="통화" xfId="4" builtinId="4"/>
-    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1189,22 +669,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" style="3" width="9.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="2" style="3" width="15.75500011" customWidth="1" outlineLevel="0"/>
-    <col min="3" max="3" style="3" width="15.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="4" style="3" width="17.12999916" customWidth="1" outlineLevel="0"/>
-    <col min="5" max="5" style="3" width="13.13000011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="3" width="13.25500011" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="7" style="3" width="14.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="8" max="8" style="3" width="11.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="9" max="16384" style="3" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="1" width="9.59765625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.296875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.09765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.59765625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1226,11 +707,11 @@
       <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1256,7 +737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1264,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4">
         <v>0.5</v>
@@ -1276,13 +757,13 @@
         <v>10</v>
       </c>
       <c r="G3" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1290,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4">
         <v>0.4</v>
@@ -1302,13 +783,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1316,7 +797,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4">
         <v>0.4</v>
@@ -1328,13 +809,13 @@
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1342,7 +823,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="4">
         <v>0.25</v>
@@ -1351,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G6" s="3">
         <v>300</v>
@@ -1360,7 +841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1368,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4">
         <v>0.5</v>
@@ -1380,13 +861,13 @@
         <v>10</v>
       </c>
       <c r="G7" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1394,7 +875,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="4">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D8" s="4">
         <v>0.4</v>
@@ -1406,13 +887,13 @@
         <v>15</v>
       </c>
       <c r="G8" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1420,7 +901,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D9" s="4">
         <v>0.4</v>
@@ -1432,13 +913,13 @@
         <v>20</v>
       </c>
       <c r="G9" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1446,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="4">
-        <v>120</v>
+        <v>1100</v>
       </c>
       <c r="D10" s="4">
         <v>0.25</v>
@@ -1455,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
@@ -1464,7 +945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1472,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4">
         <v>0.5</v>
@@ -1484,21 +965,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="3">
-        <v>20</v>
-      </c>
-      <c r="H11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="4">
-        <v>15</v>
+      <c r="C12" s="7">
+        <v>32.5</v>
       </c>
       <c r="D12" s="4">
         <v>0.4</v>
@@ -1510,13 +991,13 @@
         <v>15</v>
       </c>
       <c r="G12" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1524,7 +1005,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="4">
-        <v>20</v>
+        <v>42.5</v>
       </c>
       <c r="D13" s="4">
         <v>0.4</v>
@@ -1536,13 +1017,13 @@
         <v>20</v>
       </c>
       <c r="G13" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1550,7 +1031,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="4">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="4">
         <v>0.25</v>
@@ -1559,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G14" s="3">
         <v>300</v>
@@ -1568,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1576,7 +1057,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D15" s="4">
         <v>0.5</v>
@@ -1588,13 +1069,13 @@
         <v>10</v>
       </c>
       <c r="G15" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1602,7 +1083,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="4">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4">
         <v>0.4</v>
@@ -1614,13 +1095,13 @@
         <v>15</v>
       </c>
       <c r="G16" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1628,7 +1109,7 @@
         <v>27</v>
       </c>
       <c r="C17" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4">
         <v>0.4</v>
@@ -1640,13 +1121,13 @@
         <v>20</v>
       </c>
       <c r="G17" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1654,7 +1135,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="4">
-        <v>160</v>
+        <v>1300</v>
       </c>
       <c r="D18" s="4">
         <v>0.25</v>
@@ -1663,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G18" s="3">
         <v>300</v>
@@ -1672,7 +1153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1680,7 +1161,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4">
         <v>0.5</v>
@@ -1692,13 +1173,13 @@
         <v>10</v>
       </c>
       <c r="G19" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1706,7 +1187,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="4">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D20" s="4">
         <v>0.4</v>
@@ -1718,13 +1199,13 @@
         <v>15</v>
       </c>
       <c r="G20" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1732,7 +1213,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="4">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4">
         <v>0.4</v>
@@ -1744,13 +1225,13 @@
         <v>20</v>
       </c>
       <c r="G21" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1758,7 +1239,7 @@
         <v>32</v>
       </c>
       <c r="C22" s="4">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="D22" s="4">
         <v>0.25</v>
@@ -1767,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
@@ -1776,7 +1257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1784,7 +1265,7 @@
         <v>35</v>
       </c>
       <c r="C23" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D23" s="4">
         <v>0.5</v>
@@ -1796,13 +1277,13 @@
         <v>10</v>
       </c>
       <c r="G23" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1810,7 +1291,7 @@
         <v>33</v>
       </c>
       <c r="C24" s="4">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D24" s="4">
         <v>0.4</v>
@@ -1822,13 +1303,13 @@
         <v>15</v>
       </c>
       <c r="G24" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1836,7 +1317,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D25" s="4">
         <v>0.4</v>
@@ -1848,13 +1329,13 @@
         <v>20</v>
       </c>
       <c r="G25" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1862,7 +1343,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="4">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="D26" s="4">
         <v>0.25</v>
@@ -1871,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="4">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G26" s="3">
         <v>300</v>
@@ -1882,7 +1363,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -757,7 +757,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -783,7 +783,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -809,7 +809,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="3">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -823,7 +823,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D6" s="4">
         <v>0.25</v>
@@ -861,7 +861,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -887,7 +887,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -913,7 +913,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="3">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
@@ -927,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="4">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4">
         <v>0.25</v>
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>37</v>
@@ -991,7 +991,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>16</v>
@@ -1017,7 +1017,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
@@ -1031,7 +1031,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="4">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="D14" s="4">
         <v>0.25</v>
@@ -1069,7 +1069,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>16</v>
@@ -1095,7 +1095,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>16</v>
@@ -1121,7 +1121,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
@@ -1135,7 +1135,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="4">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="4">
         <v>0.25</v>
@@ -1173,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>16</v>
@@ -1199,7 +1199,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>16</v>
@@ -1225,7 +1225,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>16</v>
@@ -1239,7 +1239,7 @@
         <v>32</v>
       </c>
       <c r="C22" s="4">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="D22" s="4">
         <v>0.25</v>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>16</v>
@@ -1303,7 +1303,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>16</v>
@@ -1329,7 +1329,7 @@
         <v>20</v>
       </c>
       <c r="G25" s="3">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>16</v>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -823,7 +823,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="D6" s="4">
         <v>0.25</v>
@@ -927,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="4">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="D10" s="4">
         <v>0.25</v>
@@ -1031,7 +1031,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="4">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="D14" s="4">
         <v>0.25</v>
@@ -1135,7 +1135,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="4">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="D18" s="4">
         <v>0.25</v>
@@ -1239,7 +1239,7 @@
         <v>32</v>
       </c>
       <c r="C22" s="4">
-        <v>1300</v>
+        <v>4550</v>
       </c>
       <c r="D22" s="4">
         <v>0.25</v>
@@ -1343,7 +1343,7 @@
         <v>36</v>
       </c>
       <c r="C26" s="4">
-        <v>1500</v>
+        <v>5250</v>
       </c>
       <c r="D26" s="4">
         <v>0.25</v>

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E10CB7-FE23-44F2-8607-E1E3D52D917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="36" windowWidth="25752" windowHeight="11592"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -246,7 +260,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
@@ -308,7 +322,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -331,6 +345,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -343,7 +437,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -354,16 +448,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -669,23 +808,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.59765625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="15.796875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.09765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.09765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="14" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.59765625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="3" customWidth="1"/>
     <col min="9" max="9" width="9" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -711,7 +850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -724,7 +863,7 @@
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -737,624 +876,624 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="7">
         <v>25</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="7">
         <v>0.5</v>
       </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
         <v>10</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="9">
         <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="11">
         <v>30</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="11">
         <v>0.4</v>
       </c>
-      <c r="E4" s="6">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="12">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11">
         <v>15</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="13">
         <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="11">
         <v>35</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="11">
         <v>0.4</v>
       </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
         <v>20</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="13">
         <v>35</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4">
-        <v>1050</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="16">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="16">
         <v>0.25</v>
       </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="17">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16">
         <v>500</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="18">
         <v>300</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="7">
         <v>25</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="7">
         <v>0.5</v>
       </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
         <v>10</v>
       </c>
-      <c r="G7" s="3">
-        <v>25</v>
+      <c r="G7" s="9">
+        <v>20</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="11">
         <v>35</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="11">
         <v>0.4</v>
       </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8" s="12">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
         <v>15</v>
       </c>
-      <c r="G8" s="3">
-        <v>30</v>
+      <c r="G8" s="13">
+        <v>25</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="11">
         <v>40</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="11">
         <v>0.4</v>
       </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
         <v>20</v>
       </c>
-      <c r="G9" s="3">
-        <v>40</v>
+      <c r="G9" s="13">
+        <v>35</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4">
-        <v>1750</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="16">
+        <v>1500</v>
+      </c>
+      <c r="D10" s="16">
         <v>0.25</v>
       </c>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="17">
+        <v>1</v>
+      </c>
+      <c r="F10" s="16">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="18">
         <v>300</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="7">
         <v>25</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="7">
         <v>0.5</v>
       </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
         <v>10</v>
       </c>
-      <c r="G11" s="3">
-        <v>35</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="9">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="21">
         <v>32.5</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="11">
         <v>0.4</v>
       </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11">
         <v>15</v>
       </c>
-      <c r="G12" s="3">
-        <v>40</v>
+      <c r="G12" s="13">
+        <v>30</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="11">
         <v>42.5</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="11">
         <v>0.4</v>
       </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
         <v>20</v>
       </c>
-      <c r="G13" s="3">
-        <v>45</v>
+      <c r="G13" s="13">
+        <v>35</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="4">
-        <v>2800</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="16">
         <v>0.25</v>
       </c>
-      <c r="E14" s="6">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="17">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="18">
         <v>300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="7">
         <v>25</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="7">
         <v>0.5</v>
       </c>
-      <c r="E15" s="6">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
         <v>10</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="9">
+        <v>25</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="11">
         <v>35</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="D16" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
+        <v>15</v>
+      </c>
+      <c r="G16" s="13">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="11">
+        <v>50</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11">
+        <v>20</v>
+      </c>
+      <c r="G17" s="13">
         <v>35</v>
       </c>
-      <c r="D16" s="4">
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="16">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="E18" s="17">
+        <v>1</v>
+      </c>
+      <c r="F18" s="16">
+        <v>500</v>
+      </c>
+      <c r="G18" s="18">
+        <v>300</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="7">
+        <v>25</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>10</v>
+      </c>
+      <c r="G19" s="9">
+        <v>30</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="11">
+        <v>35</v>
+      </c>
+      <c r="D20" s="11">
         <v>0.4</v>
       </c>
-      <c r="E16" s="6">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="E20" s="12">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11">
         <v>15</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G20" s="13">
+        <v>35</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="11">
+        <v>55</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="12">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11">
+        <v>20</v>
+      </c>
+      <c r="G21" s="13">
         <v>40</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
+      <c r="H21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14">
+        <v>20</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="16">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="17">
+        <v>1</v>
+      </c>
+      <c r="F22" s="16">
+        <v>500</v>
+      </c>
+      <c r="G22" s="18">
+        <v>300</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="7">
+        <v>25</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7">
+        <v>10</v>
+      </c>
+      <c r="G23" s="9">
+        <v>30</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="11">
+        <v>40</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="4">
-        <v>50</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="G24" s="13">
+        <v>40</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="11">
+        <v>60</v>
+      </c>
+      <c r="D25" s="11">
         <v>0.4</v>
       </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11">
         <v>20</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G25" s="13">
         <v>45</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3500</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="H25" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="14">
+        <v>24</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="16">
+        <v>10000</v>
+      </c>
+      <c r="D26" s="16">
         <v>0.25</v>
       </c>
-      <c r="E18" s="6">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="E26" s="17">
+        <v>1</v>
+      </c>
+      <c r="F26" s="16">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
-        <v>300</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="4">
-        <v>25</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4">
-        <v>10</v>
-      </c>
-      <c r="G19" s="3">
-        <v>35</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
-        <v>18</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="4">
-        <v>35</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4">
-        <v>15</v>
-      </c>
-      <c r="G20" s="3">
-        <v>40</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="3">
-        <v>19</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="4">
-        <v>55</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4">
-        <v>20</v>
-      </c>
-      <c r="G21" s="3">
-        <v>45</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="3">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="4">
-        <v>4550</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4">
-        <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="3">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="4">
-        <v>25</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4">
-        <v>10</v>
-      </c>
-      <c r="G23" s="3">
-        <v>35</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="3">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="4">
-        <v>40</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1</v>
-      </c>
-      <c r="F24" s="4">
-        <v>15</v>
-      </c>
-      <c r="G24" s="3">
-        <v>40</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="3">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="4">
-        <v>60</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4">
-        <v>20</v>
-      </c>
-      <c r="G25" s="3">
-        <v>45</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
-        <v>24</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="4">
-        <v>5250</v>
-      </c>
-      <c r="D26" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4">
-        <v>500</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="18">
         <v>300</v>
       </c>
       <c r="H26" s="3" t="s">

--- a/Assets/Excels/enemy data.xlsx
+++ b/Assets/Excels/enemy data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E10CB7-FE23-44F2-8607-E1E3D52D917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0387AAC-D7E6-462F-9FBF-F31E88808D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -896,7 +896,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -910,10 +910,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="11">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D4" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E4" s="12">
         <v>1</v>
@@ -922,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="G4" s="13">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -936,10 +936,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D5" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
@@ -948,7 +948,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="13">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -962,16 +962,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="16">
-        <v>1000</v>
+        <v>2600</v>
       </c>
       <c r="D6" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="17">
         <v>1</v>
       </c>
       <c r="F6" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G6" s="18">
         <v>300</v>
@@ -1000,7 +1000,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -1014,10 +1014,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="11">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D8" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="13">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -1040,10 +1040,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="11">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D9" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
@@ -1052,7 +1052,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="13">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
@@ -1066,16 +1066,16 @@
         <v>20</v>
       </c>
       <c r="C10" s="16">
-        <v>1500</v>
+        <v>3500</v>
       </c>
       <c r="D10" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="17">
         <v>1</v>
       </c>
       <c r="F10" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G10" s="18">
         <v>300</v>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>37</v>
@@ -1118,10 +1118,10 @@
         <v>22</v>
       </c>
       <c r="C12" s="21">
-        <v>32.5</v>
+        <v>75</v>
       </c>
       <c r="D12" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
@@ -1130,7 +1130,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>16</v>
@@ -1144,10 +1144,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="11">
-        <v>42.5</v>
+        <v>100</v>
       </c>
       <c r="D13" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E13" s="12">
         <v>1</v>
@@ -1156,7 +1156,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="13">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>16</v>
@@ -1170,16 +1170,16 @@
         <v>24</v>
       </c>
       <c r="C14" s="16">
-        <v>2000</v>
+        <v>3750</v>
       </c>
       <c r="D14" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="17">
         <v>1</v>
       </c>
       <c r="F14" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G14" s="18">
         <v>300</v>
@@ -1208,7 +1208,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>16</v>
@@ -1222,10 +1222,10 @@
         <v>26</v>
       </c>
       <c r="C16" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="D16" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="12">
         <v>1</v>
@@ -1234,7 +1234,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>16</v>
@@ -1248,10 +1248,10 @@
         <v>27</v>
       </c>
       <c r="C17" s="11">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="D17" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E17" s="12">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="13">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>16</v>
@@ -1274,16 +1274,16 @@
         <v>28</v>
       </c>
       <c r="C18" s="16">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="D18" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="17">
         <v>1</v>
       </c>
       <c r="F18" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G18" s="18">
         <v>300</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>16</v>
@@ -1326,10 +1326,10 @@
         <v>30</v>
       </c>
       <c r="C20" s="11">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D20" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E20" s="12">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="13">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>16</v>
@@ -1352,10 +1352,10 @@
         <v>31</v>
       </c>
       <c r="C21" s="11">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D21" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E21" s="12">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>16</v>
@@ -1378,16 +1378,16 @@
         <v>32</v>
       </c>
       <c r="C22" s="16">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="D22" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E22" s="17">
         <v>1</v>
       </c>
       <c r="F22" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G22" s="18">
         <v>300</v>
@@ -1416,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>16</v>
@@ -1430,10 +1430,10 @@
         <v>33</v>
       </c>
       <c r="C24" s="11">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D24" s="11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E24" s="12">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="13">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>16</v>
@@ -1456,10 +1456,10 @@
         <v>34</v>
       </c>
       <c r="C25" s="11">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D25" s="11">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E25" s="12">
         <v>1</v>
@@ -1468,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="G25" s="13">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>16</v>
@@ -1482,16 +1482,16 @@
         <v>36</v>
       </c>
       <c r="C26" s="16">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="D26" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E26" s="17">
         <v>1</v>
       </c>
       <c r="F26" s="16">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="G26" s="18">
         <v>300</v>
